--- a/public/i-1-later/excel/実験9弦の共振エミュレータ.xlsx
+++ b/public/i-1-later/excel/実験9弦の共振エミュレータ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ogawarinkyuu/Documents/大学＿過去問/情報工学科1年/後期/2017年度工学基礎実験/エミュレータ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ogawarinkyuu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30444B7E-E5A0-2C49-8BC7-2CC617E97E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918E6F7C-38D9-6A4E-8F11-3CD59447AF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="16220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
